--- a/URIARTE 630/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/URIARTE 630/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\URIARTE 630\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F700CA-CFB0-4362-8DA8-148604471F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017A6EB8-C8F9-457C-B52A-BA911F715E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -239,16 +239,16 @@
     <t>AL LLEGAR LOS TRES MESES DE ABONO DE EXPENSAS NOS ENCONTRAMOS CON LAS FACULTADES DE DESCONECTAR A LAS UNIDADES FUNCIONALES DE LA RED DE EDESUR.</t>
   </si>
   <si>
-    <t>Liquidacion mes de OCTUBRE</t>
-  </si>
-  <si>
-    <t>Vto. 14/11</t>
-  </si>
-  <si>
     <t>TSG MES 8</t>
   </si>
   <si>
     <t>TSG MES 9</t>
+  </si>
+  <si>
+    <t>Vto. 15/12</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de NOVIEMBRE</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +376,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1037,7 +1044,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1178,7 +1185,6 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1194,29 +1200,6 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1232,6 +1215,12 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1241,6 +1230,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1609,42 +1617,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>36</v>
       </c>
@@ -1652,13 +1660,13 @@
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1666,29 +1674,29 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="109"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="108"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="47"/>
-      <c r="C12" s="108">
+      <c r="C12" s="107">
         <v>71833</v>
       </c>
       <c r="D12" s="4"/>
@@ -1699,12 +1707,12 @@
         <v>-876618.52137167996</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="47"/>
-      <c r="C13" s="108">
+      <c r="C13" s="107">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
@@ -1716,9 +1724,9 @@
         <v>900893.91845567361</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" s="47"/>
       <c r="C14" s="9">
@@ -1730,12 +1738,12 @@
       </c>
       <c r="F14" s="76">
         <f>-C38 +C32</f>
-        <v>-774498.40500000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-647471.14500000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B15" s="47"/>
       <c r="C15" s="9">
@@ -1745,68 +1753,70 @@
       <c r="E15" s="32"/>
       <c r="F15" s="76"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="47"/>
-      <c r="C16" s="9">
+      <c r="C16" s="133">
         <v>140555</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="32"/>
       <c r="F16" s="33"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="54" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="55"/>
-      <c r="C17" s="108">
-        <v>67972.039999999994</v>
+      <c r="C17" s="132">
+        <v>28784.63</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="32"/>
       <c r="F17" s="33"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="54" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="47"/>
-      <c r="C18" s="108">
+      <c r="C18" s="107">
         <v>66605.47</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="32"/>
       <c r="F18" s="33"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="54"/>
-      <c r="C19" s="108">
-        <v>230888.38</v>
+      <c r="C19" s="132">
+        <v>119278.53</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="33"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="54" t="s">
         <v>67</v>
       </c>
       <c r="B20" s="47"/>
-      <c r="C20" s="104"/>
+      <c r="C20" s="132">
+        <v>23770</v>
+      </c>
       <c r="E20" s="32"/>
       <c r="F20" s="33"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="48"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="106">
-        <f>SUM(C12:C19)</f>
-        <v>774498.40500000003</v>
+      <c r="C21" s="105">
+        <f>SUM(C12:C20)</f>
+        <v>647471.14500000002</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="34" t="s">
@@ -1814,40 +1824,40 @@
       </c>
       <c r="F21" s="35">
         <f>SUM(F12:F19)</f>
-        <v>-750223.00791600638</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-623195.74791600637</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="50" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="47"/>
-      <c r="C22" s="107"/>
+      <c r="C22" s="106"/>
       <c r="D22" s="4"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B23" s="47"/>
       <c r="C23" s="45"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="111" t="s">
+      <c r="E23" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="111"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F23" s="110"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="54"/>
       <c r="B24" s="47"/>
       <c r="C24" s="45"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="21"/>
       <c r="B25" s="22"/>
       <c r="C25" s="46">
@@ -1855,79 +1865,79 @@
         <v>0</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="79">
         <f>+C25+C21</f>
-        <v>774498.40500000003</v>
+        <v>647471.14500000002</v>
       </c>
       <c r="D26" s="4"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+    </row>
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="44"/>
       <c r="C27" s="80"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25"/>
       <c r="B29" s="19"/>
       <c r="C29" s="81"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29"/>
       <c r="B30" s="28"/>
       <c r="C30" s="82">
         <v>0</v>
       </c>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
       <c r="B31" s="37"/>
       <c r="C31" s="82">
         <v>0</v>
       </c>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="42"/>
       <c r="B32" s="43"/>
       <c r="C32" s="83"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="110"/>
-      <c r="B33" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="109"/>
+      <c r="B33" s="109"/>
       <c r="C33" s="82"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="110"/>
+      <c r="F33" s="110"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="29"/>
       <c r="B34" s="28"/>
       <c r="C34" s="82">
@@ -1935,7 +1945,7 @@
       </c>
       <c r="F34" s="5"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="38" t="s">
         <v>21</v>
       </c>
@@ -1945,84 +1955,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C36" s="82"/>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C37" s="84">
         <f>C36+C26</f>
-        <v>774498.40500000003</v>
+        <v>647471.14500000002</v>
       </c>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="39"/>
       <c r="C38" s="52">
         <f>+C26+C35</f>
-        <v>774498.40500000003</v>
+        <v>647471.14500000002</v>
       </c>
       <c r="E38" s="10"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D43" s="5"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D46" s="10"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D47" s="10"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="12"/>
       <c r="B59" s="11"/>
       <c r="C59" s="13"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -2049,56 +2059,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T118"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="0.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="14"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="0.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="130" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="120" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de OCTUBRE</v>
-      </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
+        <v>Liquidacion mes de NOVIEMBRE</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="90"/>
-      <c r="G1" s="125" t="s">
+      <c r="G1" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="128">
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="114">
         <f>Q1</f>
         <v>774498.40500000003</v>
       </c>
-      <c r="M1" s="129"/>
+      <c r="M1" s="115"/>
       <c r="Q1">
         <v>774498.40500000003</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="92" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 14/11</v>
+        <v>Vto. 15/12</v>
       </c>
       <c r="B2" s="85"/>
       <c r="C2" s="85"/>
@@ -2113,11 +2123,11 @@
       <c r="J2" s="49"/>
       <c r="K2" s="78"/>
       <c r="L2" s="78"/>
-      <c r="M2" s="105">
+      <c r="M2" s="104">
         <v>413723.43999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="93" t="s">
         <v>0</v>
       </c>
@@ -2158,7 +2168,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="93"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
@@ -2188,13 +2198,13 @@
       </c>
       <c r="L4" s="87" t="str">
         <f>A2</f>
-        <v>Vto. 14/11</v>
+        <v>Vto. 15/12</v>
       </c>
       <c r="M4" s="94" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="93">
         <v>1</v>
       </c>
@@ -2241,7 +2251,7 @@
         <v>169161.725252</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="93">
         <v>2</v>
       </c>
@@ -2289,7 +2299,7 @@
         <v>128876.534592</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="93">
         <v>3</v>
       </c>
@@ -2332,7 +2342,7 @@
         <v>169150.45165200002</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="93">
         <v>4</v>
       </c>
@@ -2375,7 +2385,7 @@
         <v>169150.45165200002</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="93">
         <v>5</v>
       </c>
@@ -2415,7 +2425,7 @@
         <v>305328.31411991996</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="96" t="s">
         <v>7</v>
       </c>
@@ -2465,49 +2475,49 @@
         <v>941667.47726792004</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="119" t="s">
+    <row r="13" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="117"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="119"/>
       <c r="J14" s="58"/>
       <c r="K14" s="59"/>
       <c r="L14" s="63"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="121" t="s">
+    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="117"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="119"/>
       <c r="J15" s="60"/>
       <c r="K15" s="61"/>
       <c r="L15" s="63"/>
@@ -2518,7 +2528,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="58"/>
       <c r="D16" s="62"/>
       <c r="E16" s="62"/>
@@ -2538,7 +2548,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" s="60" t="s">
         <v>48</v>
       </c>
@@ -2560,7 +2570,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" s="64"/>
       <c r="D18" s="65"/>
       <c r="E18" s="65"/>
@@ -2578,21 +2588,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="122" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="124"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="128"/>
       <c r="J19" s="60"/>
       <c r="K19" s="61"/>
       <c r="L19" s="63"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="60"/>
       <c r="D20" s="63"/>
       <c r="E20" s="63"/>
@@ -2610,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="60" t="s">
         <v>50</v>
       </c>
@@ -2625,13 +2635,13 @@
       </c>
       <c r="H21" s="67"/>
       <c r="I21" s="61"/>
-      <c r="J21" s="118" t="s">
+      <c r="J21" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="113"/>
+      <c r="K21" s="130"/>
       <c r="L21" s="77"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" s="60" t="s">
         <v>53</v>
       </c>
@@ -2650,7 +2660,7 @@
       <c r="K22" s="61"/>
       <c r="L22" s="63"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" s="60"/>
       <c r="D23" s="63"/>
       <c r="E23" s="63"/>
@@ -2658,11 +2668,11 @@
       <c r="G23" s="63"/>
       <c r="H23" s="63"/>
       <c r="I23" s="61"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="113"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="130"/>
       <c r="L23" s="77"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" s="74" t="s">
         <v>56</v>
       </c>
@@ -2679,7 +2689,7 @@
       <c r="K24" s="61"/>
       <c r="L24" s="63"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
@@ -2696,7 +2706,7 @@
       <c r="K25" s="61"/>
       <c r="L25" s="63"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" s="75" t="s">
         <v>37</v>
       </c>
@@ -2713,7 +2723,7 @@
       <c r="K26" s="61"/>
       <c r="L26" s="63"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" s="75" t="s">
         <v>40</v>
       </c>
@@ -2730,7 +2740,7 @@
       <c r="K27" s="61"/>
       <c r="L27" s="63"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="75" t="s">
         <v>38</v>
       </c>
@@ -2747,7 +2757,7 @@
       <c r="K28" s="61"/>
       <c r="L28" s="63"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="D29" s="63"/>
       <c r="E29" s="63"/>
       <c r="F29" s="63"/>
@@ -2758,7 +2768,7 @@
       <c r="K29" s="61"/>
       <c r="L29" s="63"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" s="75" t="s">
         <v>44</v>
       </c>
@@ -2775,7 +2785,7 @@
       <c r="K30" s="61"/>
       <c r="L30" s="63"/>
     </row>
-    <row r="31" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="60"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
@@ -2787,55 +2797,55 @@
       <c r="K31" s="70"/>
       <c r="L31" s="63"/>
     </row>
-    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="114" t="s">
+    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
-      <c r="H32" s="116">
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="118">
         <f>SUM(H24:H31)</f>
         <v>200266.06350000002</v>
       </c>
-      <c r="I32" s="117"/>
+      <c r="I32" s="119"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
       <c r="L32" s="63"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="119" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C36" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="120"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
-      <c r="H36" s="120"/>
-      <c r="I36" s="117"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="119"/>
       <c r="J36" s="58"/>
       <c r="K36" s="59"/>
       <c r="L36" s="63"/>
     </row>
-    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="121" t="s">
+    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="117"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="124"/>
+      <c r="H37" s="124"/>
+      <c r="I37" s="119"/>
       <c r="J37" s="60"/>
       <c r="K37" s="61"/>
       <c r="L37" s="63"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" s="58"/>
       <c r="D38" s="62"/>
       <c r="E38" s="62"/>
@@ -2849,7 +2859,7 @@
       <c r="K38" s="61"/>
       <c r="L38" s="63"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" s="60" t="s">
         <v>48</v>
       </c>
@@ -2866,7 +2876,7 @@
       <c r="K39" s="61"/>
       <c r="L39" s="63"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" s="64"/>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -2878,21 +2888,21 @@
       <c r="K40" s="61"/>
       <c r="L40" s="63"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="122" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="123"/>
-      <c r="E41" s="123"/>
-      <c r="F41" s="123"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="123"/>
-      <c r="I41" s="124"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="128"/>
       <c r="J41" s="60"/>
       <c r="K41" s="61"/>
       <c r="L41" s="63"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" s="60"/>
       <c r="D42" s="63"/>
       <c r="E42" s="63"/>
@@ -2904,7 +2914,7 @@
       <c r="K42" s="61"/>
       <c r="L42" s="63"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
@@ -2919,13 +2929,13 @@
       </c>
       <c r="H43" s="67"/>
       <c r="I43" s="61"/>
-      <c r="J43" s="118" t="s">
+      <c r="J43" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="113"/>
+      <c r="K43" s="130"/>
       <c r="L43" s="77"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" s="60" t="s">
         <v>53</v>
       </c>
@@ -2944,7 +2954,7 @@
       <c r="K44" s="61"/>
       <c r="L44" s="63"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="60"/>
       <c r="D45" s="63"/>
       <c r="E45" s="63"/>
@@ -2952,11 +2962,11 @@
       <c r="G45" s="63"/>
       <c r="H45" s="63"/>
       <c r="I45" s="61"/>
-      <c r="J45" s="112"/>
-      <c r="K45" s="113"/>
+      <c r="J45" s="131"/>
+      <c r="K45" s="130"/>
       <c r="L45" s="77"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="60" t="s">
         <v>56</v>
       </c>
@@ -2973,7 +2983,7 @@
       <c r="K46" s="61"/>
       <c r="L46" s="63"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="60"/>
       <c r="D47" s="63"/>
       <c r="E47" s="63"/>
@@ -2985,7 +2995,7 @@
       <c r="K47" s="61"/>
       <c r="L47" s="63"/>
     </row>
-    <row r="48" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="60"/>
       <c r="D48" s="63"/>
       <c r="E48" s="63"/>
@@ -2997,54 +3007,54 @@
       <c r="K48" s="70"/>
       <c r="L48" s="63"/>
     </row>
-    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="114" t="s">
+    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="115"/>
-      <c r="E49" s="115"/>
-      <c r="F49" s="115"/>
-      <c r="G49" s="115"/>
-      <c r="H49" s="116">
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="118">
         <f>M6</f>
         <v>128876.534592</v>
       </c>
-      <c r="I49" s="117"/>
+      <c r="I49" s="119"/>
       <c r="J49" s="71"/>
       <c r="K49" s="72"/>
       <c r="L49" s="63"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="119" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C52" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="120"/>
-      <c r="E52" s="120"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="120"/>
-      <c r="H52" s="120"/>
-      <c r="I52" s="117"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="124"/>
+      <c r="G52" s="124"/>
+      <c r="H52" s="124"/>
+      <c r="I52" s="119"/>
       <c r="J52" s="58"/>
       <c r="K52" s="59"/>
       <c r="L52" s="63"/>
     </row>
-    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="121" t="s">
+    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C53" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="120"/>
-      <c r="E53" s="120"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="120"/>
-      <c r="I53" s="117"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="124"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="124"/>
+      <c r="I53" s="119"/>
       <c r="J53" s="60"/>
       <c r="K53" s="61"/>
       <c r="L53" s="63"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C54" s="58"/>
       <c r="D54" s="62"/>
       <c r="E54" s="62"/>
@@ -3058,7 +3068,7 @@
       <c r="K54" s="61"/>
       <c r="L54" s="63"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C55" s="60" t="s">
         <v>48</v>
       </c>
@@ -3075,7 +3085,7 @@
       <c r="K55" s="61"/>
       <c r="L55" s="63"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" s="64"/>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -3087,21 +3097,21 @@
       <c r="K56" s="61"/>
       <c r="L56" s="63"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="122" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="123"/>
-      <c r="E57" s="123"/>
-      <c r="F57" s="123"/>
-      <c r="G57" s="123"/>
-      <c r="H57" s="123"/>
-      <c r="I57" s="124"/>
+      <c r="D57" s="127"/>
+      <c r="E57" s="127"/>
+      <c r="F57" s="127"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="127"/>
+      <c r="I57" s="128"/>
       <c r="J57" s="60"/>
       <c r="K57" s="61"/>
       <c r="L57" s="63"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" s="60"/>
       <c r="D58" s="63"/>
       <c r="E58" s="63"/>
@@ -3113,7 +3123,7 @@
       <c r="K58" s="61"/>
       <c r="L58" s="63"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" s="60" t="s">
         <v>50</v>
       </c>
@@ -3128,13 +3138,13 @@
       </c>
       <c r="H59" s="67"/>
       <c r="I59" s="61"/>
-      <c r="J59" s="118" t="s">
+      <c r="J59" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K59" s="113"/>
+      <c r="K59" s="130"/>
       <c r="L59" s="77"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" s="60" t="s">
         <v>53</v>
       </c>
@@ -3153,7 +3163,7 @@
       <c r="K60" s="61"/>
       <c r="L60" s="63"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C61" s="60"/>
       <c r="D61" s="63"/>
       <c r="E61" s="63"/>
@@ -3161,11 +3171,11 @@
       <c r="G61" s="63"/>
       <c r="H61" s="63"/>
       <c r="I61" s="61"/>
-      <c r="J61" s="112"/>
-      <c r="K61" s="113"/>
+      <c r="J61" s="131"/>
+      <c r="K61" s="130"/>
       <c r="L61" s="77"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C62" s="60" t="s">
         <v>56</v>
       </c>
@@ -3182,7 +3192,7 @@
       <c r="K62" s="61"/>
       <c r="L62" s="63"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C63" s="75" t="s">
         <v>39</v>
       </c>
@@ -3199,7 +3209,7 @@
       <c r="K63" s="61"/>
       <c r="L63" s="63"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C64" s="75" t="s">
         <v>37</v>
       </c>
@@ -3216,7 +3226,7 @@
       <c r="K64" s="61"/>
       <c r="L64" s="63"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C65" s="75" t="s">
         <v>40</v>
       </c>
@@ -3233,7 +3243,7 @@
       <c r="K65" s="61"/>
       <c r="L65" s="63"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C66" s="75" t="s">
         <v>38</v>
       </c>
@@ -3250,7 +3260,7 @@
       <c r="K66" s="61"/>
       <c r="L66" s="63"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D67" s="63"/>
       <c r="E67" s="63"/>
       <c r="F67" s="63"/>
@@ -3261,7 +3271,7 @@
       <c r="K67" s="61"/>
       <c r="L67" s="63"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="75" t="s">
         <v>44</v>
       </c>
@@ -3278,7 +3288,7 @@
       <c r="K68" s="61"/>
       <c r="L68" s="63"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="60"/>
       <c r="D69" s="63"/>
       <c r="E69" s="63"/>
@@ -3290,7 +3300,7 @@
       <c r="K69" s="61"/>
       <c r="L69" s="63"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C70" s="60"/>
       <c r="D70" s="63"/>
       <c r="E70" s="63"/>
@@ -3302,7 +3312,7 @@
       <c r="K70" s="61"/>
       <c r="L70" s="63"/>
     </row>
-    <row r="71" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C71" s="60"/>
       <c r="D71" s="63"/>
       <c r="E71" s="63"/>
@@ -3314,55 +3324,55 @@
       <c r="K71" s="70"/>
       <c r="L71" s="63"/>
     </row>
-    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="114" t="s">
+    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C72" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="115"/>
-      <c r="E72" s="115"/>
-      <c r="F72" s="115"/>
-      <c r="G72" s="115"/>
-      <c r="H72" s="116">
+      <c r="D72" s="117"/>
+      <c r="E72" s="117"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="117"/>
+      <c r="H72" s="118">
         <f>SUM(H62:H71)</f>
         <v>200266.06350000002</v>
       </c>
-      <c r="I72" s="117"/>
+      <c r="I72" s="119"/>
       <c r="J72" s="71"/>
       <c r="K72" s="72"/>
       <c r="L72" s="63"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="119" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C76" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="120"/>
-      <c r="E76" s="120"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="120"/>
-      <c r="H76" s="120"/>
-      <c r="I76" s="117"/>
+      <c r="D76" s="124"/>
+      <c r="E76" s="124"/>
+      <c r="F76" s="124"/>
+      <c r="G76" s="124"/>
+      <c r="H76" s="124"/>
+      <c r="I76" s="119"/>
       <c r="J76" s="58"/>
       <c r="K76" s="59"/>
       <c r="L76" s="63"/>
     </row>
-    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="121" t="s">
+    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C77" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="120"/>
-      <c r="E77" s="120"/>
-      <c r="F77" s="120"/>
-      <c r="G77" s="120"/>
-      <c r="H77" s="120"/>
-      <c r="I77" s="117"/>
+      <c r="D77" s="124"/>
+      <c r="E77" s="124"/>
+      <c r="F77" s="124"/>
+      <c r="G77" s="124"/>
+      <c r="H77" s="124"/>
+      <c r="I77" s="119"/>
       <c r="J77" s="60"/>
       <c r="K77" s="61"/>
       <c r="L77" s="63"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C78" s="58"/>
       <c r="D78" s="62"/>
       <c r="E78" s="62"/>
@@ -3376,7 +3386,7 @@
       <c r="K78" s="61"/>
       <c r="L78" s="63"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C79" s="60" t="s">
         <v>48</v>
       </c>
@@ -3393,7 +3403,7 @@
       <c r="K79" s="61"/>
       <c r="L79" s="63"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C80" s="64"/>
       <c r="D80" s="65"/>
       <c r="E80" s="65"/>
@@ -3405,21 +3415,21 @@
       <c r="K80" s="61"/>
       <c r="L80" s="63"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="122" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D81" s="123"/>
-      <c r="E81" s="123"/>
-      <c r="F81" s="123"/>
-      <c r="G81" s="123"/>
-      <c r="H81" s="123"/>
-      <c r="I81" s="124"/>
+      <c r="D81" s="127"/>
+      <c r="E81" s="127"/>
+      <c r="F81" s="127"/>
+      <c r="G81" s="127"/>
+      <c r="H81" s="127"/>
+      <c r="I81" s="128"/>
       <c r="J81" s="60"/>
       <c r="K81" s="61"/>
       <c r="L81" s="63"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C82" s="60"/>
       <c r="D82" s="63"/>
       <c r="E82" s="63"/>
@@ -3431,7 +3441,7 @@
       <c r="K82" s="61"/>
       <c r="L82" s="63"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C83" s="60" t="s">
         <v>50</v>
       </c>
@@ -3446,13 +3456,13 @@
       </c>
       <c r="H83" s="67"/>
       <c r="I83" s="61"/>
-      <c r="J83" s="118" t="s">
+      <c r="J83" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K83" s="113"/>
+      <c r="K83" s="130"/>
       <c r="L83" s="77"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C84" s="60" t="s">
         <v>53</v>
       </c>
@@ -3471,7 +3481,7 @@
       <c r="K84" s="61"/>
       <c r="L84" s="63"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C85" s="60"/>
       <c r="D85" s="63"/>
       <c r="E85" s="63"/>
@@ -3479,11 +3489,11 @@
       <c r="G85" s="63"/>
       <c r="H85" s="63"/>
       <c r="I85" s="61"/>
-      <c r="J85" s="112"/>
-      <c r="K85" s="113"/>
+      <c r="J85" s="131"/>
+      <c r="K85" s="130"/>
       <c r="L85" s="77"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C86" s="60" t="s">
         <v>56</v>
       </c>
@@ -3500,7 +3510,7 @@
       <c r="K86" s="61"/>
       <c r="L86" s="63"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C87" s="75" t="s">
         <v>39</v>
       </c>
@@ -3517,7 +3527,7 @@
       <c r="K87" s="61"/>
       <c r="L87" s="63"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C88" s="75" t="s">
         <v>37</v>
       </c>
@@ -3534,7 +3544,7 @@
       <c r="K88" s="61"/>
       <c r="L88" s="63"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C89" s="75" t="s">
         <v>40</v>
       </c>
@@ -3551,7 +3561,7 @@
       <c r="K89" s="61"/>
       <c r="L89" s="63"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="75" t="s">
         <v>38</v>
       </c>
@@ -3568,7 +3578,7 @@
       <c r="K90" s="61"/>
       <c r="L90" s="63"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D91" s="63"/>
       <c r="E91" s="63"/>
       <c r="F91" s="63"/>
@@ -3579,7 +3589,7 @@
       <c r="K91" s="61"/>
       <c r="L91" s="63"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C92" s="75" t="s">
         <v>44</v>
       </c>
@@ -3596,7 +3606,7 @@
       <c r="K92" s="70"/>
       <c r="L92" s="63"/>
     </row>
-    <row r="93" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D93" s="63"/>
       <c r="E93" s="63"/>
       <c r="F93" s="63"/>
@@ -3607,55 +3617,55 @@
       <c r="K93" s="61"/>
       <c r="L93" s="63"/>
     </row>
-    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="114" t="s">
+    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C94" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D94" s="115"/>
-      <c r="E94" s="115"/>
-      <c r="F94" s="115"/>
-      <c r="G94" s="115"/>
-      <c r="H94" s="116">
+      <c r="D94" s="117"/>
+      <c r="E94" s="117"/>
+      <c r="F94" s="117"/>
+      <c r="G94" s="117"/>
+      <c r="H94" s="118">
         <f>SUM(H86:H93)</f>
         <v>200266.06350000002</v>
       </c>
-      <c r="I94" s="117"/>
+      <c r="I94" s="119"/>
       <c r="J94" s="71"/>
       <c r="K94" s="72"/>
       <c r="L94" s="63"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="119" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C98" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="120"/>
-      <c r="E98" s="120"/>
-      <c r="F98" s="120"/>
-      <c r="G98" s="120"/>
-      <c r="H98" s="120"/>
-      <c r="I98" s="117"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="124"/>
+      <c r="F98" s="124"/>
+      <c r="G98" s="124"/>
+      <c r="H98" s="124"/>
+      <c r="I98" s="119"/>
       <c r="J98" s="58"/>
       <c r="K98" s="59"/>
       <c r="L98" s="63"/>
     </row>
-    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="121" t="s">
+    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C99" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="120"/>
-      <c r="E99" s="120"/>
-      <c r="F99" s="120"/>
-      <c r="G99" s="120"/>
-      <c r="H99" s="120"/>
-      <c r="I99" s="117"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="124"/>
+      <c r="H99" s="124"/>
+      <c r="I99" s="119"/>
       <c r="J99" s="60"/>
       <c r="K99" s="61"/>
       <c r="L99" s="63"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C100" s="58"/>
       <c r="D100" s="62"/>
       <c r="E100" s="62"/>
@@ -3669,7 +3679,7 @@
       <c r="K100" s="61"/>
       <c r="L100" s="63"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C101" s="60" t="s">
         <v>48</v>
       </c>
@@ -3686,7 +3696,7 @@
       <c r="K101" s="61"/>
       <c r="L101" s="63"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C102" s="64"/>
       <c r="D102" s="65"/>
       <c r="E102" s="65"/>
@@ -3698,21 +3708,21 @@
       <c r="K102" s="61"/>
       <c r="L102" s="63"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="122" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D103" s="123"/>
-      <c r="E103" s="123"/>
-      <c r="F103" s="123"/>
-      <c r="G103" s="123"/>
-      <c r="H103" s="123"/>
-      <c r="I103" s="124"/>
+      <c r="D103" s="127"/>
+      <c r="E103" s="127"/>
+      <c r="F103" s="127"/>
+      <c r="G103" s="127"/>
+      <c r="H103" s="127"/>
+      <c r="I103" s="128"/>
       <c r="J103" s="60"/>
       <c r="K103" s="61"/>
       <c r="L103" s="63"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C104" s="60"/>
       <c r="D104" s="63"/>
       <c r="E104" s="63"/>
@@ -3724,7 +3734,7 @@
       <c r="K104" s="61"/>
       <c r="L104" s="63"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C105" s="60" t="s">
         <v>50</v>
       </c>
@@ -3739,13 +3749,13 @@
       </c>
       <c r="H105" s="67"/>
       <c r="I105" s="61"/>
-      <c r="J105" s="118" t="s">
+      <c r="J105" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K105" s="113"/>
+      <c r="K105" s="130"/>
       <c r="L105" s="77"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C106" s="60" t="s">
         <v>53</v>
       </c>
@@ -3763,7 +3773,7 @@
       <c r="K106" s="61"/>
       <c r="L106" s="63"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C107" s="60"/>
       <c r="D107" s="63"/>
       <c r="E107" s="63"/>
@@ -3771,11 +3781,11 @@
       <c r="G107" s="63"/>
       <c r="H107" s="63"/>
       <c r="I107" s="61"/>
-      <c r="J107" s="112"/>
-      <c r="K107" s="113"/>
+      <c r="J107" s="131"/>
+      <c r="K107" s="130"/>
       <c r="L107" s="77"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C108" s="60" t="s">
         <v>56</v>
       </c>
@@ -3792,7 +3802,7 @@
       <c r="K108" s="61"/>
       <c r="L108" s="63"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C109" s="75" t="s">
         <v>39</v>
       </c>
@@ -3809,7 +3819,7 @@
       <c r="K109" s="61"/>
       <c r="L109" s="63"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C110" s="75" t="s">
         <v>37</v>
       </c>
@@ -3826,7 +3836,7 @@
       <c r="K110" s="61"/>
       <c r="L110" s="63"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C111" s="75" t="s">
         <v>40</v>
       </c>
@@ -3843,7 +3853,7 @@
       <c r="K111" s="61"/>
       <c r="L111" s="63"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C112" s="75" t="s">
         <v>38</v>
       </c>
@@ -3860,7 +3870,7 @@
       <c r="K112" s="61"/>
       <c r="L112" s="63"/>
     </row>
-    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D113" s="63"/>
       <c r="E113" s="63"/>
       <c r="F113" s="63"/>
@@ -3871,7 +3881,7 @@
       <c r="K113" s="61"/>
       <c r="L113" s="63"/>
     </row>
-    <row r="114" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C114" s="75" t="s">
         <v>44</v>
       </c>
@@ -3888,7 +3898,7 @@
       <c r="K114" s="70"/>
       <c r="L114" s="63"/>
     </row>
-    <row r="115" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D115" s="63"/>
       <c r="E115" s="63"/>
       <c r="F115" s="63"/>
@@ -3899,27 +3909,50 @@
       <c r="K115" s="61"/>
       <c r="L115" s="63"/>
     </row>
-    <row r="116" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="114" t="s">
+    <row r="116" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C116" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D116" s="115"/>
-      <c r="E116" s="115"/>
-      <c r="F116" s="115"/>
-      <c r="G116" s="115"/>
-      <c r="H116" s="116">
+      <c r="D116" s="117"/>
+      <c r="E116" s="117"/>
+      <c r="F116" s="117"/>
+      <c r="G116" s="117"/>
+      <c r="H116" s="118">
         <f>SUM(H108:H115)</f>
         <v>200266.06350000002</v>
       </c>
-      <c r="I116" s="117"/>
+      <c r="I116" s="119"/>
       <c r="J116" s="71"/>
       <c r="K116" s="72"/>
       <c r="L116" s="63"/>
     </row>
-    <row r="117" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3936,29 +3969,6 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
